--- a/9_asistencia_evaluacion/matricula_asistencia_notas_Caucasia_2026-2.xlsx
+++ b/9_asistencia_evaluacion/matricula_asistencia_notas_Caucasia_2026-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documentos\extension\camino-udea\9_asistencia_evaluacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B794A4C-689C-4D43-86EC-C140409F423E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976D838E-FADD-465B-908A-D4B3EF9CCB01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inscritos" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="107">
   <si>
     <t>METODOLOGÍA DE ESTUDIO</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>Walter Antonio Perez Guzman</t>
+  </si>
+  <si>
+    <t>perezguzmanwalterantonio14@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -798,7 +801,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -925,6 +928,99 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -955,15 +1051,6 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1009,87 +1096,6 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1190,10 +1196,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="16" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1689,28 +1691,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="102"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="103"/>
     </row>
     <row r="2" spans="1:8" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
@@ -2096,7 +2098,7 @@
         <v>1033261244</v>
       </c>
       <c r="E20" s="14"/>
-      <c r="F20" s="133">
+      <c r="F20">
         <v>3215036126</v>
       </c>
       <c r="G20" s="43" t="s">
@@ -2162,7 +2164,7 @@
         <v>1038116237</v>
       </c>
       <c r="E23" s="14"/>
-      <c r="F23" s="133">
+      <c r="F23">
         <v>3147879724</v>
       </c>
       <c r="G23" s="43" t="s">
@@ -2507,11 +2509,19 @@
       <c r="B39" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
+      <c r="C39" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="15">
+        <v>1040502849</v>
+      </c>
       <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="17"/>
+      <c r="F39" s="14">
+        <v>3218908879</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>106</v>
+      </c>
       <c r="H39" s="14"/>
     </row>
     <row r="40" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -2845,172 +2855,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="110" t="s">
+      <c r="B1" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
-      <c r="AC1" s="110"/>
-      <c r="AD1" s="110"/>
-      <c r="AE1" s="110"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
+      <c r="V1" s="111"/>
+      <c r="W1" s="111"/>
+      <c r="X1" s="111"/>
+      <c r="Y1" s="111"/>
+      <c r="Z1" s="111"/>
+      <c r="AA1" s="111"/>
+      <c r="AB1" s="111"/>
+      <c r="AC1" s="111"/>
+      <c r="AD1" s="111"/>
+      <c r="AE1" s="111"/>
     </row>
     <row r="2" spans="1:31" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="126" t="s">
+      <c r="D2" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="111" t="s">
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="112"/>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="120" t="s">
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="113"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="121"/>
-      <c r="T2" s="121"/>
-      <c r="U2" s="121"/>
-      <c r="V2" s="121"/>
-      <c r="W2" s="121"/>
-      <c r="X2" s="121"/>
-      <c r="Y2" s="121"/>
-      <c r="Z2" s="122"/>
-      <c r="AA2" s="103" t="s">
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
+      <c r="U2" s="122"/>
+      <c r="V2" s="122"/>
+      <c r="W2" s="122"/>
+      <c r="X2" s="122"/>
+      <c r="Y2" s="122"/>
+      <c r="Z2" s="123"/>
+      <c r="AA2" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="AB2" s="104"/>
-      <c r="AC2" s="104"/>
-      <c r="AD2" s="104"/>
-      <c r="AE2" s="105"/>
+      <c r="AB2" s="105"/>
+      <c r="AC2" s="105"/>
+      <c r="AD2" s="105"/>
+      <c r="AE2" s="106"/>
     </row>
     <row r="3" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="98"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="129" t="s">
+      <c r="A3" s="74"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="114" t="s">
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
+      <c r="H3" s="132"/>
+      <c r="I3" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="115"/>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="116"/>
-      <c r="R3" s="123" t="s">
+      <c r="J3" s="116"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="116"/>
+      <c r="P3" s="116"/>
+      <c r="Q3" s="117"/>
+      <c r="R3" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="124"/>
-      <c r="T3" s="124"/>
-      <c r="U3" s="124"/>
-      <c r="V3" s="124"/>
-      <c r="W3" s="124"/>
-      <c r="X3" s="124"/>
-      <c r="Y3" s="124"/>
-      <c r="Z3" s="125"/>
-      <c r="AA3" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="107"/>
-      <c r="AC3" s="107"/>
-      <c r="AD3" s="107"/>
-      <c r="AE3" s="108"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="125"/>
+      <c r="W3" s="125"/>
+      <c r="X3" s="125"/>
+      <c r="Y3" s="125"/>
+      <c r="Z3" s="126"/>
+      <c r="AA3" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="108"/>
+      <c r="AC3" s="108"/>
+      <c r="AD3" s="108"/>
+      <c r="AE3" s="109"/>
     </row>
     <row r="4" spans="1:31" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="98"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="132" t="s">
+      <c r="A4" s="74"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="120"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="117" t="s">
+      <c r="I4" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118"/>
-      <c r="P4" s="119"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="119"/>
+      <c r="M4" s="119"/>
+      <c r="N4" s="119"/>
+      <c r="O4" s="119"/>
+      <c r="P4" s="120"/>
       <c r="Q4" s="3"/>
-      <c r="R4" s="117" t="s">
+      <c r="R4" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="118"/>
-      <c r="X4" s="118"/>
-      <c r="Y4" s="119"/>
+      <c r="S4" s="119"/>
+      <c r="T4" s="119"/>
+      <c r="U4" s="119"/>
+      <c r="V4" s="119"/>
+      <c r="W4" s="119"/>
+      <c r="X4" s="119"/>
+      <c r="Y4" s="120"/>
       <c r="Z4" s="12"/>
-      <c r="AA4" s="109" t="s">
+      <c r="AA4" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="AB4" s="109"/>
-      <c r="AC4" s="109"/>
-      <c r="AD4" s="109"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="110"/>
       <c r="AE4" s="3"/>
     </row>
     <row r="5" spans="1:31" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
-      <c r="B5" s="96"/>
-      <c r="C5" s="98"/>
+      <c r="A5" s="74"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="74"/>
       <c r="D5" s="33"/>
       <c r="E5" s="33"/>
       <c r="F5" s="33"/>
@@ -3018,16 +3028,16 @@
       <c r="H5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="134">
+      <c r="I5" s="44">
         <v>46258</v>
       </c>
-      <c r="J5" s="134">
+      <c r="J5" s="44">
         <v>46259</v>
       </c>
-      <c r="K5" s="134">
+      <c r="K5" s="44">
         <v>46260</v>
       </c>
-      <c r="L5" s="134">
+      <c r="L5" s="44">
         <v>46261</v>
       </c>
       <c r="M5" s="28"/>
@@ -4921,7 +4931,7 @@
       </c>
       <c r="C41" s="21">
         <f>+Inscritos!D39</f>
-        <v>0</v>
+        <v>1040502849</v>
       </c>
       <c r="D41" s="13"/>
       <c r="E41" s="13"/>
@@ -6288,123 +6298,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="72.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
     </row>
     <row r="2" spans="1:20" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="72" t="str">
+      <c r="D2" s="45" t="str">
         <f>Asistencia!D2</f>
         <v>NOMBRE DOCENTE</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="72" t="str">
+      <c r="E2" s="46"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="45" t="str">
         <f>Asistencia!I2</f>
         <v>NOMBRE DOCENTE</v>
       </c>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="72" t="s">
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="72" t="str">
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="45" t="str">
         <f>Asistencia!AA2</f>
         <v>NOMBRE DOCENTE</v>
       </c>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="74"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="47"/>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="82"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="89" t="s">
+      <c r="A3" s="58"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="90"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="83" t="s">
+      <c r="E3" s="66"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="66" t="s">
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="77"/>
+      <c r="M3" s="95"/>
+      <c r="N3" s="95"/>
+      <c r="O3" s="95"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="50"/>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="82"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="92"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="70"/>
-      <c r="O4" s="70"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="78"/>
-      <c r="R4" s="79"/>
-      <c r="S4" s="79"/>
-      <c r="T4" s="80"/>
+      <c r="A4" s="58"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="99"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="53"/>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="82"/>
-      <c r="B5" s="96"/>
-      <c r="C5" s="98"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="74"/>
       <c r="D5" s="22">
         <v>0.75</v>
       </c>
@@ -7945,7 +7955,7 @@
       </c>
       <c r="C41" s="18">
         <f>+Inscritos!D39</f>
-        <v>0</v>
+        <v>1040502849</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -8986,195 +8996,186 @@
       </c>
     </row>
     <row r="66" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D66" s="48" t="s">
+      <c r="D66" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="E66" s="51" t="s">
+      <c r="E66" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="G66" s="45" t="s">
+      <c r="G66" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="H66" s="60" t="s">
+      <c r="H66" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="I66" s="60" t="s">
+      <c r="I66" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="J66" s="45" t="s">
+      <c r="J66" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L66" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="M66" s="57" t="s">
+      <c r="M66" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="N66" s="57" t="s">
+      <c r="N66" s="85" t="s">
         <v>10</v>
       </c>
       <c r="O66" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="Q66" s="63" t="s">
+      <c r="Q66" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="R66" s="63" t="s">
+      <c r="R66" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="S66" s="63" t="s">
+      <c r="S66" s="91" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D67" s="49"/>
-      <c r="E67" s="52"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="61"/>
-      <c r="I67" s="61"/>
-      <c r="J67" s="46"/>
+      <c r="D67" s="80"/>
+      <c r="E67" s="83"/>
+      <c r="G67" s="77"/>
+      <c r="H67" s="89"/>
+      <c r="I67" s="89"/>
+      <c r="J67" s="77"/>
       <c r="L67" s="55"/>
-      <c r="M67" s="58"/>
-      <c r="N67" s="58"/>
+      <c r="M67" s="86"/>
+      <c r="N67" s="86"/>
       <c r="O67" s="55"/>
-      <c r="Q67" s="64"/>
-      <c r="R67" s="64"/>
-      <c r="S67" s="64"/>
+      <c r="Q67" s="92"/>
+      <c r="R67" s="92"/>
+      <c r="S67" s="92"/>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D68" s="49"/>
-      <c r="E68" s="52"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="61"/>
-      <c r="I68" s="61"/>
-      <c r="J68" s="46"/>
+      <c r="D68" s="80"/>
+      <c r="E68" s="83"/>
+      <c r="G68" s="77"/>
+      <c r="H68" s="89"/>
+      <c r="I68" s="89"/>
+      <c r="J68" s="77"/>
       <c r="L68" s="55"/>
-      <c r="M68" s="58"/>
-      <c r="N68" s="58"/>
+      <c r="M68" s="86"/>
+      <c r="N68" s="86"/>
       <c r="O68" s="55"/>
-      <c r="Q68" s="64"/>
-      <c r="R68" s="64"/>
-      <c r="S68" s="64"/>
+      <c r="Q68" s="92"/>
+      <c r="R68" s="92"/>
+      <c r="S68" s="92"/>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D69" s="49"/>
-      <c r="E69" s="52"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="61"/>
-      <c r="I69" s="61"/>
-      <c r="J69" s="46"/>
+      <c r="D69" s="80"/>
+      <c r="E69" s="83"/>
+      <c r="G69" s="77"/>
+      <c r="H69" s="89"/>
+      <c r="I69" s="89"/>
+      <c r="J69" s="77"/>
       <c r="L69" s="55"/>
-      <c r="M69" s="58"/>
-      <c r="N69" s="58"/>
+      <c r="M69" s="86"/>
+      <c r="N69" s="86"/>
       <c r="O69" s="55"/>
-      <c r="Q69" s="64"/>
-      <c r="R69" s="64"/>
-      <c r="S69" s="64"/>
+      <c r="Q69" s="92"/>
+      <c r="R69" s="92"/>
+      <c r="S69" s="92"/>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D70" s="49"/>
-      <c r="E70" s="52"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="61"/>
-      <c r="I70" s="61"/>
-      <c r="J70" s="46"/>
+      <c r="D70" s="80"/>
+      <c r="E70" s="83"/>
+      <c r="G70" s="77"/>
+      <c r="H70" s="89"/>
+      <c r="I70" s="89"/>
+      <c r="J70" s="77"/>
       <c r="L70" s="55"/>
-      <c r="M70" s="58"/>
-      <c r="N70" s="58"/>
+      <c r="M70" s="86"/>
+      <c r="N70" s="86"/>
       <c r="O70" s="55"/>
-      <c r="Q70" s="64"/>
-      <c r="R70" s="64"/>
-      <c r="S70" s="64"/>
+      <c r="Q70" s="92"/>
+      <c r="R70" s="92"/>
+      <c r="S70" s="92"/>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D71" s="49"/>
-      <c r="E71" s="52"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="61"/>
-      <c r="I71" s="61"/>
-      <c r="J71" s="46"/>
+      <c r="D71" s="80"/>
+      <c r="E71" s="83"/>
+      <c r="G71" s="77"/>
+      <c r="H71" s="89"/>
+      <c r="I71" s="89"/>
+      <c r="J71" s="77"/>
       <c r="L71" s="55"/>
-      <c r="M71" s="58"/>
-      <c r="N71" s="58"/>
+      <c r="M71" s="86"/>
+      <c r="N71" s="86"/>
       <c r="O71" s="55"/>
-      <c r="Q71" s="64"/>
-      <c r="R71" s="64"/>
-      <c r="S71" s="64"/>
+      <c r="Q71" s="92"/>
+      <c r="R71" s="92"/>
+      <c r="S71" s="92"/>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D72" s="49"/>
-      <c r="E72" s="52"/>
-      <c r="G72" s="46"/>
-      <c r="H72" s="61"/>
-      <c r="I72" s="61"/>
-      <c r="J72" s="46"/>
+      <c r="D72" s="80"/>
+      <c r="E72" s="83"/>
+      <c r="G72" s="77"/>
+      <c r="H72" s="89"/>
+      <c r="I72" s="89"/>
+      <c r="J72" s="77"/>
       <c r="L72" s="55"/>
-      <c r="M72" s="58"/>
-      <c r="N72" s="58"/>
+      <c r="M72" s="86"/>
+      <c r="N72" s="86"/>
       <c r="O72" s="55"/>
-      <c r="Q72" s="64"/>
-      <c r="R72" s="64"/>
-      <c r="S72" s="64"/>
+      <c r="Q72" s="92"/>
+      <c r="R72" s="92"/>
+      <c r="S72" s="92"/>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D73" s="49"/>
-      <c r="E73" s="52"/>
-      <c r="G73" s="46"/>
-      <c r="H73" s="61"/>
-      <c r="I73" s="61"/>
-      <c r="J73" s="46"/>
+      <c r="D73" s="80"/>
+      <c r="E73" s="83"/>
+      <c r="G73" s="77"/>
+      <c r="H73" s="89"/>
+      <c r="I73" s="89"/>
+      <c r="J73" s="77"/>
       <c r="L73" s="55"/>
-      <c r="M73" s="58"/>
-      <c r="N73" s="58"/>
+      <c r="M73" s="86"/>
+      <c r="N73" s="86"/>
       <c r="O73" s="55"/>
-      <c r="Q73" s="64"/>
-      <c r="R73" s="64"/>
-      <c r="S73" s="64"/>
+      <c r="Q73" s="92"/>
+      <c r="R73" s="92"/>
+      <c r="S73" s="92"/>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D74" s="49"/>
-      <c r="E74" s="52"/>
-      <c r="G74" s="46"/>
-      <c r="H74" s="61"/>
-      <c r="I74" s="61"/>
-      <c r="J74" s="46"/>
+      <c r="D74" s="80"/>
+      <c r="E74" s="83"/>
+      <c r="G74" s="77"/>
+      <c r="H74" s="89"/>
+      <c r="I74" s="89"/>
+      <c r="J74" s="77"/>
       <c r="L74" s="55"/>
-      <c r="M74" s="58"/>
-      <c r="N74" s="58"/>
+      <c r="M74" s="86"/>
+      <c r="N74" s="86"/>
       <c r="O74" s="55"/>
-      <c r="Q74" s="64"/>
-      <c r="R74" s="64"/>
-      <c r="S74" s="64"/>
+      <c r="Q74" s="92"/>
+      <c r="R74" s="92"/>
+      <c r="S74" s="92"/>
     </row>
     <row r="75" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D75" s="50"/>
-      <c r="E75" s="53"/>
-      <c r="G75" s="47"/>
-      <c r="H75" s="62"/>
-      <c r="I75" s="62"/>
-      <c r="J75" s="47"/>
+      <c r="D75" s="81"/>
+      <c r="E75" s="84"/>
+      <c r="G75" s="78"/>
+      <c r="H75" s="90"/>
+      <c r="I75" s="90"/>
+      <c r="J75" s="78"/>
       <c r="L75" s="56"/>
-      <c r="M75" s="59"/>
-      <c r="N75" s="59"/>
+      <c r="M75" s="87"/>
+      <c r="N75" s="87"/>
       <c r="O75" s="56"/>
-      <c r="Q75" s="65"/>
-      <c r="R75" s="65"/>
-      <c r="S75" s="65"/>
+      <c r="Q75" s="93"/>
+      <c r="R75" s="93"/>
+      <c r="S75" s="93"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:T60">
     <sortCondition ref="B6"/>
   </sortState>
   <mergeCells count="25">
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="Q3:T4"/>
-    <mergeCell ref="O66:O75"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="G3:K4"/>
-    <mergeCell ref="D3:F4"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="J66:J75"/>
     <mergeCell ref="D66:D75"/>
@@ -9191,6 +9192,15 @@
     <mergeCell ref="I66:I75"/>
     <mergeCell ref="Q2:T2"/>
     <mergeCell ref="L2:P2"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="Q3:T4"/>
+    <mergeCell ref="O66:O75"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="G3:K4"/>
+    <mergeCell ref="D3:F4"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C2:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/9_asistencia_evaluacion/matricula_asistencia_notas_Caucasia_2026-2.xlsx
+++ b/9_asistencia_evaluacion/matricula_asistencia_notas_Caucasia_2026-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documentos\extension\camino-udea\9_asistencia_evaluacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976D838E-FADD-465B-908A-D4B3EF9CCB01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F23D9A-971A-4006-9C7E-7C5292FE94A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="116">
   <si>
     <t>METODOLOGÍA DE ESTUDIO</t>
   </si>
@@ -223,9 +223,6 @@
     <t xml:space="preserve">Federman Benitez López </t>
   </si>
   <si>
-    <t>JUAN DIEGO  CUETO PALLARES</t>
-  </si>
-  <si>
     <t>MARIA INES VERGARA MANGONES</t>
   </si>
   <si>
@@ -256,18 +253,9 @@
     <t>Jeronimorestrepoe616@gmail.com</t>
   </si>
   <si>
-    <t>veleriaruizgarcia47@gmail.com</t>
-  </si>
-  <si>
-    <t>ggildegar@gmail.com</t>
-  </si>
-  <si>
     <t>Rektalejo@gmail.com</t>
   </si>
   <si>
-    <t>Vickyposada86@gmail.com</t>
-  </si>
-  <si>
     <t>arrietajohanandres45@gmail.com</t>
   </si>
   <si>
@@ -277,9 +265,6 @@
     <t>juanpablorodriguezrestrepi@gmail.com</t>
   </si>
   <si>
-    <t>analiamendez643@gmil.com</t>
-  </si>
-  <si>
     <t>npaterninasanchez@gmail.com</t>
   </si>
   <si>
@@ -310,9 +295,6 @@
     <t>samuelmupa3@gamil.com</t>
   </si>
   <si>
-    <t>dsierrap28@gmail.com</t>
-  </si>
-  <si>
     <t>juandavidremolinavargas916@gmail.com</t>
   </si>
   <si>
@@ -340,12 +322,6 @@
     <t>Paolavasquezflor@gmail.com</t>
   </si>
   <si>
-    <t>federmaanbenitez43@gmail.com</t>
-  </si>
-  <si>
-    <t>mmabel.gandia@gmail.com</t>
-  </si>
-  <si>
     <t>marivergara0803@gmail.com</t>
   </si>
   <si>
@@ -359,13 +335,64 @@
   </si>
   <si>
     <t>perezguzmanwalterantonio14@gmail.com</t>
+  </si>
+  <si>
+    <t>juandavidpastranamestra@gmail.com</t>
+  </si>
+  <si>
+    <t>federmanbenitez43@gmail.com</t>
+  </si>
+  <si>
+    <t>posadaescobar008@gmail.com</t>
+  </si>
+  <si>
+    <t>manucamargourzola23@gmail.com</t>
+  </si>
+  <si>
+    <t>Elizabeth ibañez londoño</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cedula </t>
+  </si>
+  <si>
+    <t>ibanezelizabeth777@gmail.com</t>
+  </si>
+  <si>
+    <t>melanybueno784@gmail.com</t>
+  </si>
+  <si>
+    <t>juancuet@icloud.com</t>
+  </si>
+  <si>
+    <t>Juan Diego Cueto Pallares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cédula </t>
+  </si>
+  <si>
+    <t>analiamendez643@gmail.com</t>
+  </si>
+  <si>
+    <t>valeriaruizgarcia47@gmail.com</t>
+  </si>
+  <si>
+    <t>john fredy manchego valencia</t>
+  </si>
+  <si>
+    <t>212audiovisual@gmail.com</t>
+  </si>
+  <si>
+    <t>Luz Marina Mieles Nisperuza</t>
+  </si>
+  <si>
+    <t>marinamieles26@hotmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -513,6 +540,14 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -797,11 +832,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -931,6 +967,211 @@
     <xf numFmtId="16" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -958,15 +1199,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1009,197 +1241,9 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -1691,28 +1735,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="103"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
@@ -1722,7 +1766,7 @@
         <v>27</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>14</v>
@@ -1748,7 +1792,7 @@
         <v>34</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D4" s="43">
         <v>1038115585</v>
@@ -1758,7 +1802,7 @@
         <v>3001723573</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H4" s="14"/>
     </row>
@@ -1770,7 +1814,7 @@
         <v>45</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5" s="43">
         <v>1192464442</v>
@@ -1780,7 +1824,7 @@
         <v>3122581841</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H5" s="14"/>
     </row>
@@ -1792,7 +1836,7 @@
         <v>58</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="43">
         <v>1001158202</v>
@@ -1802,7 +1846,7 @@
         <v>3113963182</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H6" s="14"/>
     </row>
@@ -1814,7 +1858,7 @@
         <v>56</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D7" s="43">
         <v>1038117571</v>
@@ -1824,7 +1868,7 @@
         <v>6048149274</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H7" s="14"/>
     </row>
@@ -1836,7 +1880,7 @@
         <v>39</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" s="43">
         <v>1062440365</v>
@@ -1845,8 +1889,8 @@
       <c r="F8" s="43">
         <v>3143281112</v>
       </c>
-      <c r="G8" s="43" t="s">
-        <v>79</v>
+      <c r="G8" s="46" t="s">
+        <v>110</v>
       </c>
       <c r="H8" s="14"/>
     </row>
@@ -1858,7 +1902,7 @@
         <v>30</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D9" s="43">
         <v>1103505811</v>
@@ -1868,7 +1912,7 @@
         <v>3044664111</v>
       </c>
       <c r="G9" s="43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H9" s="14"/>
     </row>
@@ -1880,7 +1924,7 @@
         <v>47</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="43">
         <v>1038101556</v>
@@ -1890,7 +1934,7 @@
         <v>3217605804</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H10" s="14"/>
     </row>
@@ -1902,7 +1946,7 @@
         <v>57</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D11" s="43">
         <v>1038115269</v>
@@ -1912,7 +1956,7 @@
         <v>3124327847</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H11" s="14"/>
     </row>
@@ -1920,21 +1964,21 @@
       <c r="A12" s="10">
         <v>9</v>
       </c>
-      <c r="B12" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="43">
-        <v>1001534767</v>
+      <c r="B12" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="15">
+        <v>1038109715</v>
       </c>
       <c r="E12" s="14"/>
-      <c r="F12" s="43">
-        <v>3135411067</v>
-      </c>
-      <c r="G12" s="43" t="s">
-        <v>100</v>
+      <c r="F12" s="14">
+        <v>3217589181</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>105</v>
       </c>
       <c r="H12" s="14"/>
     </row>
@@ -1943,20 +1987,20 @@
         <v>10</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" s="43">
-        <v>1038113945</v>
+        <v>1001534767</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="43">
-        <v>3107298876</v>
-      </c>
-      <c r="G13" s="43" t="s">
-        <v>94</v>
+        <v>3135411067</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>100</v>
       </c>
       <c r="H13" s="14"/>
     </row>
@@ -1965,20 +2009,20 @@
         <v>11</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="C14" s="43" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="43">
-        <v>1038107680</v>
+        <v>1038113945</v>
       </c>
       <c r="E14" s="14"/>
       <c r="F14" s="43">
-        <v>3137172886</v>
+        <v>3107298876</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H14" s="14"/>
     </row>
@@ -1987,20 +2031,20 @@
         <v>12</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" s="43">
-        <v>1040875356</v>
+        <v>1038107680</v>
       </c>
       <c r="E15" s="14"/>
       <c r="F15" s="43">
-        <v>3106229584</v>
+        <v>3137172886</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H15" s="14"/>
     </row>
@@ -2009,20 +2053,20 @@
         <v>13</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D16" s="43">
-        <v>1038115504</v>
+        <v>1040875356</v>
       </c>
       <c r="E16" s="14"/>
       <c r="F16" s="43">
-        <v>3136498443</v>
+        <v>3106229584</v>
       </c>
       <c r="G16" s="43" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="H16" s="14"/>
     </row>
@@ -2031,20 +2075,20 @@
         <v>14</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" s="43">
-        <v>1038117645</v>
+        <v>1038115504</v>
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="43">
-        <v>3235097353</v>
+        <v>3136498443</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="H17" s="14"/>
     </row>
@@ -2053,20 +2097,20 @@
         <v>15</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>65</v>
       </c>
       <c r="D18" s="43">
-        <v>1038103169</v>
+        <v>1038117645</v>
       </c>
       <c r="E18" s="14"/>
       <c r="F18" s="43">
-        <v>3165842276</v>
+        <v>3235097353</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H18" s="14"/>
     </row>
@@ -2074,35 +2118,43 @@
       <c r="A19" s="10">
         <v>16</v>
       </c>
-      <c r="B19" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
+      <c r="B19" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="43">
+        <v>1038103169</v>
+      </c>
       <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="17"/>
+      <c r="F19" s="43">
+        <v>3165842276</v>
+      </c>
+      <c r="G19" s="43" t="s">
+        <v>72</v>
+      </c>
       <c r="H19" s="14"/>
     </row>
     <row r="20" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>17</v>
       </c>
-      <c r="B20" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="43">
-        <v>1033261244</v>
+      <c r="B20" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1067891152</v>
       </c>
       <c r="E20" s="14"/>
-      <c r="F20">
-        <v>3215036126</v>
-      </c>
-      <c r="G20" s="43" t="s">
-        <v>91</v>
+      <c r="F20" s="47">
+        <v>3229543712</v>
+      </c>
+      <c r="G20" s="45" t="s">
+        <v>99</v>
       </c>
       <c r="H20" s="14"/>
     </row>
@@ -2111,20 +2163,20 @@
         <v>18</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D21" s="43">
-        <v>1063287705</v>
+        <v>1033261244</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="43">
-        <v>3117154382</v>
+        <v>3215036126</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="H21" s="14"/>
     </row>
@@ -2133,20 +2185,20 @@
         <v>19</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="D22" s="43">
-        <v>1025894485</v>
+        <v>1063287705</v>
       </c>
       <c r="E22" s="14"/>
       <c r="F22" s="43">
-        <v>3052516415</v>
-      </c>
-      <c r="G22" s="43" t="s">
-        <v>78</v>
+        <v>3143350597</v>
+      </c>
+      <c r="G22" s="46" t="s">
+        <v>107</v>
       </c>
       <c r="H22" s="14"/>
     </row>
@@ -2155,20 +2207,20 @@
         <v>20</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D23" s="43">
-        <v>1038116237</v>
+        <v>1025894485</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23">
-        <v>3147879724</v>
+        <v>3052516415</v>
       </c>
       <c r="G23" s="43" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H23" s="14"/>
     </row>
@@ -2177,19 +2229,19 @@
         <v>21</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C24" s="43" t="s">
         <v>65</v>
       </c>
       <c r="D24" s="43">
-        <v>1007470866</v>
+        <v>1038116237</v>
       </c>
       <c r="E24" s="14"/>
       <c r="F24" s="43">
-        <v>3105226442</v>
-      </c>
-      <c r="G24" s="43" t="s">
+        <v>3147879724</v>
+      </c>
+      <c r="G24" s="46" t="s">
         <v>102</v>
       </c>
       <c r="H24" s="14"/>
@@ -2199,20 +2251,20 @@
         <v>22</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D25" s="43">
-        <v>1042826278</v>
+        <v>1007470866</v>
       </c>
       <c r="E25" s="14"/>
       <c r="F25" s="43">
-        <v>3214595235</v>
+        <v>3105226442</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H25" s="14"/>
     </row>
@@ -2221,20 +2273,20 @@
         <v>23</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C26" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D26" s="43">
-        <v>1038114475</v>
+        <v>1042826278</v>
       </c>
       <c r="E26" s="14"/>
       <c r="F26" s="43">
-        <v>3207003213</v>
+        <v>3214595235</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H26" s="14"/>
     </row>
@@ -2243,20 +2295,20 @@
         <v>24</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D27" s="43">
-        <v>1038115335</v>
+        <v>1038114475</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="43">
-        <v>3103923438</v>
-      </c>
-      <c r="G27" s="43" t="s">
-        <v>93</v>
+        <v>3103853588</v>
+      </c>
+      <c r="G27" s="46" t="s">
+        <v>106</v>
       </c>
       <c r="H27" s="14"/>
     </row>
@@ -2265,20 +2317,20 @@
         <v>25</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D28" s="43">
-        <v>1065889467</v>
+        <v>1038115335</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="43">
-        <v>3018130343</v>
+        <v>3103923438</v>
       </c>
       <c r="G28" s="43" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H28" s="14"/>
     </row>
@@ -2287,20 +2339,20 @@
         <v>26</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C29" s="43" t="s">
         <v>65</v>
       </c>
       <c r="D29" s="43">
-        <v>1003305257</v>
+        <v>1065889467</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="43">
-        <v>3004508837</v>
+        <v>3018130343</v>
       </c>
       <c r="G29" s="43" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="H29" s="14"/>
     </row>
@@ -2309,20 +2361,20 @@
         <v>27</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D30" s="43">
-        <v>1066517127</v>
+        <v>1003305257</v>
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="43">
-        <v>3108048269</v>
+        <v>3004508837</v>
       </c>
       <c r="G30" s="43" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H30" s="14"/>
     </row>
@@ -2331,20 +2383,20 @@
         <v>28</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C31" s="43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D31" s="43">
-        <v>1038110741</v>
+        <v>1066517127</v>
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="43">
-        <v>3217695233</v>
+        <v>3108048269</v>
       </c>
       <c r="G31" s="43" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H31" s="14"/>
     </row>
@@ -2353,20 +2405,20 @@
         <v>29</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C32" s="43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D32" s="43">
-        <v>1038130180</v>
+        <v>1038110741</v>
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="43">
-        <v>3127679340</v>
-      </c>
-      <c r="G32" s="43" t="s">
-        <v>83</v>
+        <v>3217695233</v>
+      </c>
+      <c r="G32" s="46" t="s">
+        <v>101</v>
       </c>
       <c r="H32" s="14"/>
     </row>
@@ -2375,20 +2427,20 @@
         <v>30</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" s="43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D33" s="43">
-        <v>1038115649</v>
+        <v>1038130180</v>
       </c>
       <c r="E33" s="14"/>
       <c r="F33" s="43">
-        <v>3104933206</v>
+        <v>3127679340</v>
       </c>
       <c r="G33" s="43" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H33" s="14"/>
     </row>
@@ -2397,20 +2449,20 @@
         <v>31</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C34" s="43" t="s">
         <v>65</v>
       </c>
       <c r="D34" s="43">
-        <v>1038648764</v>
+        <v>1038115649</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="43">
-        <v>3132068325</v>
+        <v>3104933206</v>
       </c>
       <c r="G34" s="43" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H34" s="14"/>
     </row>
@@ -2419,20 +2471,20 @@
         <v>32</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C35" s="43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D35" s="43">
-        <v>1038118107</v>
+        <v>1038648764</v>
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="43">
-        <v>3125629643</v>
+        <v>3132068325</v>
       </c>
       <c r="G35" s="43" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H35" s="14"/>
     </row>
@@ -2440,21 +2492,21 @@
       <c r="A36" s="10">
         <v>33</v>
       </c>
-      <c r="B36" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" s="43">
-        <v>1020303245</v>
+      <c r="B36" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="15">
+        <v>1038648764</v>
       </c>
       <c r="E36" s="14"/>
-      <c r="F36" s="43">
-        <v>3132893979</v>
-      </c>
-      <c r="G36" s="43" t="s">
-        <v>81</v>
+      <c r="F36" s="14">
+        <v>3132068325</v>
+      </c>
+      <c r="G36" s="45" t="s">
+        <v>68</v>
       </c>
       <c r="H36" s="14"/>
     </row>
@@ -2463,20 +2515,20 @@
         <v>34</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C37" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D37" s="43">
-        <v>1045143166</v>
+        <v>1038118107</v>
       </c>
       <c r="E37" s="14"/>
       <c r="F37" s="43">
-        <v>3145252170</v>
+        <v>3125629643</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H37" s="14"/>
     </row>
@@ -2485,20 +2537,20 @@
         <v>35</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C38" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D38" s="43">
-        <v>1038116526</v>
+        <v>1020303245</v>
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="43">
-        <v>3332364722</v>
+        <v>3132893979</v>
       </c>
       <c r="G38" s="43" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H38" s="14"/>
     </row>
@@ -2506,21 +2558,21 @@
       <c r="A39" s="10">
         <v>36</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>105</v>
+      <c r="B39" s="43" t="s">
+        <v>42</v>
       </c>
       <c r="C39" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="D39" s="15">
-        <v>1040502849</v>
+        <v>65</v>
+      </c>
+      <c r="D39" s="43">
+        <v>1045143166</v>
       </c>
       <c r="E39" s="14"/>
-      <c r="F39" s="14">
-        <v>3218908879</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>106</v>
+      <c r="F39" s="43">
+        <v>3145252170</v>
+      </c>
+      <c r="G39" s="43" t="s">
+        <v>77</v>
       </c>
       <c r="H39" s="14"/>
     </row>
@@ -2529,20 +2581,20 @@
         <v>37</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C40" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" s="43" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="D40" s="43">
+        <v>1038116526</v>
       </c>
       <c r="E40" s="14"/>
-      <c r="F40" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="G40" s="43" t="s">
-        <v>95</v>
+      <c r="F40" s="43">
+        <v>3332364722</v>
+      </c>
+      <c r="G40" s="46" t="s">
+        <v>111</v>
       </c>
       <c r="H40" s="14"/>
     </row>
@@ -2550,48 +2602,88 @@
       <c r="A41" s="10">
         <v>38</v>
       </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
+      <c r="B41" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" s="15">
+        <v>1040502849</v>
+      </c>
       <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="17"/>
+      <c r="F41" s="14">
+        <v>3218908879</v>
+      </c>
+      <c r="G41" s="17" t="s">
+        <v>98</v>
+      </c>
       <c r="H41" s="14"/>
     </row>
     <row r="42" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <v>39</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
+      <c r="B42" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="43" t="s">
+        <v>66</v>
+      </c>
       <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="17"/>
+      <c r="F42" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="G42" s="43" t="s">
+        <v>89</v>
+      </c>
       <c r="H42" s="14"/>
     </row>
     <row r="43" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10">
         <v>40</v>
       </c>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
+      <c r="B43" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" s="15">
+        <v>1038125682</v>
+      </c>
       <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="17"/>
+      <c r="F43" s="14">
+        <v>3116434791</v>
+      </c>
+      <c r="G43" s="45" t="s">
+        <v>113</v>
+      </c>
       <c r="H43" s="14"/>
     </row>
     <row r="44" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="10">
         <v>41</v>
       </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
+      <c r="B44" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" s="15">
+        <v>33104650</v>
+      </c>
       <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="17"/>
+      <c r="F44" s="14">
+        <v>31466565745</v>
+      </c>
+      <c r="G44" s="45" t="s">
+        <v>115</v>
+      </c>
       <c r="H44" s="14"/>
     </row>
     <row r="45" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -2823,17 +2915,31 @@
       <c r="H63" s="14"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:H40">
-    <sortCondition ref="B4:B40"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:H42">
+    <sortCondition ref="B4:B42"/>
   </sortState>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G20" r:id="rId1" xr:uid="{68FA5FC2-8ADC-47B3-993E-2A13D83AE5E1}"/>
+    <hyperlink ref="G13" r:id="rId2" xr:uid="{C5973669-08D4-4EDB-BC88-68C473FA1CE3}"/>
+    <hyperlink ref="G32" r:id="rId3" xr:uid="{3BD91535-3D01-463C-8CCA-D89045539993}"/>
+    <hyperlink ref="G24" r:id="rId4" xr:uid="{746370CC-A7A7-415A-A5E9-F6AFD8BF2B1F}"/>
+    <hyperlink ref="G36" r:id="rId5" xr:uid="{B1EF5833-1719-4014-9B02-97215BECB266}"/>
+    <hyperlink ref="G12" r:id="rId6" xr:uid="{1A57B07E-8E3A-46FF-8553-08EAA206C617}"/>
+    <hyperlink ref="G27" r:id="rId7" xr:uid="{C24D9F3D-2654-4B54-990D-FC0A5F15A97D}"/>
+    <hyperlink ref="G22" r:id="rId8" xr:uid="{8C70339C-1B33-4C80-BB8E-6C1DAC47D612}"/>
+    <hyperlink ref="G8" r:id="rId9" xr:uid="{7410146B-0C3D-43D1-B729-BE5671A1A2B1}"/>
+    <hyperlink ref="G40" r:id="rId10" xr:uid="{A6D3AE4C-77D8-4128-87E1-5474F08EADEB}"/>
+    <hyperlink ref="G43" r:id="rId11" xr:uid="{54BDB88E-CE45-4C75-86A6-A24DF4F78D4D}"/>
+    <hyperlink ref="G44" r:id="rId12" xr:uid="{F9BDA904-CAE2-409A-A474-5CB00EEA97A8}"/>
+  </hyperlinks>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup scale="80" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup scale="80" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId13"/>
+  <drawing r:id="rId14"/>
 </worksheet>
 </file>
 
@@ -2855,172 +2961,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
-      <c r="V1" s="111"/>
-      <c r="W1" s="111"/>
-      <c r="X1" s="111"/>
-      <c r="Y1" s="111"/>
-      <c r="Z1" s="111"/>
-      <c r="AA1" s="111"/>
-      <c r="AB1" s="111"/>
-      <c r="AC1" s="111"/>
-      <c r="AD1" s="111"/>
-      <c r="AE1" s="111"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+      <c r="T1" s="59"/>
+      <c r="U1" s="59"/>
+      <c r="V1" s="59"/>
+      <c r="W1" s="59"/>
+      <c r="X1" s="59"/>
+      <c r="Y1" s="59"/>
+      <c r="Z1" s="59"/>
+      <c r="AA1" s="59"/>
+      <c r="AB1" s="59"/>
+      <c r="AC1" s="59"/>
+      <c r="AD1" s="59"/>
+      <c r="AE1" s="59"/>
     </row>
     <row r="2" spans="1:31" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="127" t="s">
+      <c r="D2" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="112" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="121" t="s">
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="122"/>
-      <c r="T2" s="122"/>
-      <c r="U2" s="122"/>
-      <c r="V2" s="122"/>
-      <c r="W2" s="122"/>
-      <c r="X2" s="122"/>
-      <c r="Y2" s="122"/>
-      <c r="Z2" s="123"/>
-      <c r="AA2" s="104" t="s">
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="72"/>
+      <c r="Y2" s="72"/>
+      <c r="Z2" s="73"/>
+      <c r="AA2" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="AB2" s="105"/>
-      <c r="AC2" s="105"/>
-      <c r="AD2" s="105"/>
-      <c r="AE2" s="106"/>
+      <c r="AB2" s="53"/>
+      <c r="AC2" s="53"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="54"/>
     </row>
     <row r="3" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="74"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="130" t="s">
+      <c r="A3" s="61"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="132"/>
-      <c r="I3" s="115" t="s">
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="116"/>
-      <c r="N3" s="116"/>
-      <c r="O3" s="116"/>
-      <c r="P3" s="116"/>
-      <c r="Q3" s="117"/>
-      <c r="R3" s="124" t="s">
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="S3" s="125"/>
-      <c r="T3" s="125"/>
-      <c r="U3" s="125"/>
-      <c r="V3" s="125"/>
-      <c r="W3" s="125"/>
-      <c r="X3" s="125"/>
-      <c r="Y3" s="125"/>
-      <c r="Z3" s="126"/>
-      <c r="AA3" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="108"/>
-      <c r="AC3" s="108"/>
-      <c r="AD3" s="108"/>
-      <c r="AE3" s="109"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="75"/>
+      <c r="V3" s="75"/>
+      <c r="W3" s="75"/>
+      <c r="X3" s="75"/>
+      <c r="Y3" s="75"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="56"/>
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="56"/>
+      <c r="AE3" s="57"/>
     </row>
     <row r="4" spans="1:31" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="74"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="133" t="s">
+      <c r="A4" s="61"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="120"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="70"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="118" t="s">
+      <c r="I4" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="119"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="120"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="70"/>
       <c r="Q4" s="3"/>
-      <c r="R4" s="118" t="s">
+      <c r="R4" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="S4" s="119"/>
-      <c r="T4" s="119"/>
-      <c r="U4" s="119"/>
-      <c r="V4" s="119"/>
-      <c r="W4" s="119"/>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="120"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="69"/>
+      <c r="V4" s="69"/>
+      <c r="W4" s="69"/>
+      <c r="X4" s="69"/>
+      <c r="Y4" s="70"/>
       <c r="Z4" s="12"/>
-      <c r="AA4" s="110" t="s">
+      <c r="AA4" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="110"/>
+      <c r="AB4" s="58"/>
+      <c r="AC4" s="58"/>
+      <c r="AD4" s="58"/>
       <c r="AE4" s="3"/>
     </row>
     <row r="5" spans="1:31" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="74"/>
-      <c r="B5" s="72"/>
-      <c r="C5" s="74"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="61"/>
       <c r="D5" s="33"/>
       <c r="E5" s="33"/>
       <c r="F5" s="33"/>
@@ -3496,11 +3602,11 @@
       </c>
       <c r="B14" s="18" t="str">
         <f>+Inscritos!B12</f>
-        <v xml:space="preserve">Federman Benitez López </v>
+        <v>Elizabeth ibañez londoño</v>
       </c>
       <c r="C14" s="21">
         <f>+Inscritos!D12</f>
-        <v>1001534767</v>
+        <v>1038109715</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
@@ -3549,11 +3655,11 @@
       </c>
       <c r="B15" s="18" t="str">
         <f>+Inscritos!B13</f>
-        <v>Gabriela Arenas Sánchez</v>
+        <v xml:space="preserve">Federman Benitez López </v>
       </c>
       <c r="C15" s="21">
         <f>+Inscritos!D13</f>
-        <v>1038113945</v>
+        <v>1001534767</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
@@ -3602,11 +3708,11 @@
       </c>
       <c r="B16" s="18" t="str">
         <f>+Inscritos!B14</f>
-        <v>Isabella  Balza Estrada</v>
+        <v>Gabriela Arenas Sánchez</v>
       </c>
       <c r="C16" s="21">
         <f>+Inscritos!D14</f>
-        <v>1038107680</v>
+        <v>1038113945</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -3655,11 +3761,11 @@
       </c>
       <c r="B17" s="18" t="str">
         <f>+Inscritos!B15</f>
-        <v>Jerónimo  Restrepo Echeberry</v>
+        <v>Isabella  Balza Estrada</v>
       </c>
       <c r="C17" s="21">
         <f>+Inscritos!D15</f>
-        <v>1040875356</v>
+        <v>1038107680</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -3708,11 +3814,11 @@
       </c>
       <c r="B18" s="18" t="str">
         <f>+Inscritos!B16</f>
-        <v>Jerónimo Gil, Guerra</v>
+        <v>Jerónimo  Restrepo Echeberry</v>
       </c>
       <c r="C18" s="21">
         <f>+Inscritos!D16</f>
-        <v>1038115504</v>
+        <v>1040875356</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -3761,11 +3867,11 @@
       </c>
       <c r="B19" s="18" t="str">
         <f>+Inscritos!B17</f>
-        <v>Jhon Alexander Torres Posada</v>
+        <v>Jerónimo Gil, Guerra</v>
       </c>
       <c r="C19" s="21">
         <f>+Inscritos!D17</f>
-        <v>1038117645</v>
+        <v>1038115504</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
@@ -3814,11 +3920,11 @@
       </c>
       <c r="B20" s="18" t="str">
         <f>+Inscritos!B18</f>
-        <v>Johan Andrés  Arrieta Meneses</v>
+        <v>Jhon Alexander Torres Posada</v>
       </c>
       <c r="C20" s="21">
         <f>+Inscritos!D18</f>
-        <v>1038103169</v>
+        <v>1038117645</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -3867,11 +3973,11 @@
       </c>
       <c r="B21" s="18" t="str">
         <f>+Inscritos!B19</f>
-        <v>Juan David Pastrana Verona</v>
+        <v>Johan Andrés  Arrieta Meneses</v>
       </c>
       <c r="C21" s="21">
         <f>+Inscritos!D19</f>
-        <v>0</v>
+        <v>1038103169</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
@@ -3920,11 +4026,11 @@
       </c>
       <c r="B22" s="18" t="str">
         <f>+Inscritos!B20</f>
-        <v>juan david remolina vargas</v>
+        <v>Juan David Pastrana Verona</v>
       </c>
       <c r="C22" s="21">
         <f>+Inscritos!D20</f>
-        <v>1033261244</v>
+        <v>1067891152</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
@@ -3935,7 +4041,9 @@
         <v>0</v>
       </c>
       <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
+      <c r="J22" s="38">
+        <v>1</v>
+      </c>
       <c r="K22" s="38"/>
       <c r="L22" s="38"/>
       <c r="M22" s="38"/>
@@ -3944,7 +4052,7 @@
       <c r="P22" s="38"/>
       <c r="Q22" s="37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="R22" s="38"/>
       <c r="S22" s="38"/>
@@ -3973,11 +4081,11 @@
       </c>
       <c r="B23" s="18" t="str">
         <f>+Inscritos!B21</f>
-        <v>JUAN DIEGO  CUETO PALLARES</v>
+        <v>juan david remolina vargas</v>
       </c>
       <c r="C23" s="21">
         <f>+Inscritos!D21</f>
-        <v>1063287705</v>
+        <v>1033261244</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
@@ -4026,11 +4134,11 @@
       </c>
       <c r="B24" s="18" t="str">
         <f>+Inscritos!B22</f>
-        <v xml:space="preserve">Juan Pablo Rodriguez Restrepo </v>
+        <v>Juan Diego Cueto Pallares</v>
       </c>
       <c r="C24" s="21">
         <f>+Inscritos!D22</f>
-        <v>1025894485</v>
+        <v>1063287705</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
@@ -4079,11 +4187,11 @@
       </c>
       <c r="B25" s="18" t="str">
         <f>+Inscritos!B23</f>
-        <v>Manuela Carmargo Merlano</v>
+        <v xml:space="preserve">Juan Pablo Rodriguez Restrepo </v>
       </c>
       <c r="C25" s="21">
         <f>+Inscritos!D23</f>
-        <v>1038116237</v>
+        <v>1025894485</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
@@ -4132,11 +4240,11 @@
       </c>
       <c r="B26" s="18" t="str">
         <f>+Inscritos!B24</f>
-        <v>MARIA INES VERGARA MANGONES</v>
+        <v>Manuela Carmargo Merlano</v>
       </c>
       <c r="C26" s="21">
         <f>+Inscritos!D24</f>
-        <v>1007470866</v>
+        <v>1038116237</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
@@ -4185,11 +4293,11 @@
       </c>
       <c r="B27" s="18" t="str">
         <f>+Inscritos!B25</f>
-        <v xml:space="preserve">Martín  Araujo Vásquez </v>
+        <v>MARIA INES VERGARA MANGONES</v>
       </c>
       <c r="C27" s="21">
         <f>+Inscritos!D25</f>
-        <v>1042826278</v>
+        <v>1007470866</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
@@ -4238,11 +4346,11 @@
       </c>
       <c r="B28" s="18" t="str">
         <f>+Inscritos!B26</f>
-        <v xml:space="preserve">Melany Bueno Sierra </v>
+        <v xml:space="preserve">Martín  Araujo Vásquez </v>
       </c>
       <c r="C28" s="21">
         <f>+Inscritos!D26</f>
-        <v>1038114475</v>
+        <v>1042826278</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
@@ -4291,11 +4399,11 @@
       </c>
       <c r="B29" s="18" t="str">
         <f>+Inscritos!B27</f>
-        <v xml:space="preserve">Melissa Ceballos Serpa </v>
+        <v xml:space="preserve">Melany Bueno Sierra </v>
       </c>
       <c r="C29" s="21">
         <f>+Inscritos!D27</f>
-        <v>1038115335</v>
+        <v>1038114475</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
@@ -4344,11 +4452,11 @@
       </c>
       <c r="B30" s="18" t="str">
         <f>+Inscritos!B28</f>
-        <v xml:space="preserve">Nikoll Paternina Sánchez </v>
+        <v xml:space="preserve">Melissa Ceballos Serpa </v>
       </c>
       <c r="C30" s="21">
         <f>+Inscritos!D28</f>
-        <v>1065889467</v>
+        <v>1038115335</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
@@ -4397,11 +4505,11 @@
       </c>
       <c r="B31" s="18" t="str">
         <f>+Inscritos!B29</f>
-        <v>Rousse Peralta</v>
+        <v xml:space="preserve">Nikoll Paternina Sánchez </v>
       </c>
       <c r="C31" s="21">
         <f>+Inscritos!D29</f>
-        <v>1003305257</v>
+        <v>1065889467</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
@@ -4450,11 +4558,11 @@
       </c>
       <c r="B32" s="18" t="str">
         <f>+Inscritos!B30</f>
-        <v xml:space="preserve">Samuel  Muñoz </v>
+        <v>Rousse Peralta</v>
       </c>
       <c r="C32" s="21">
         <f>+Inscritos!D30</f>
-        <v>1066517127</v>
+        <v>1003305257</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
@@ -4503,11 +4611,11 @@
       </c>
       <c r="B33" s="18" t="str">
         <f>+Inscritos!B31</f>
-        <v>Samuel Escobar Posada</v>
+        <v xml:space="preserve">Samuel  Muñoz </v>
       </c>
       <c r="C33" s="21">
         <f>+Inscritos!D31</f>
-        <v>1038110741</v>
+        <v>1066517127</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
@@ -4556,11 +4664,11 @@
       </c>
       <c r="B34" s="18" t="str">
         <f>+Inscritos!B32</f>
-        <v>Santiago  Gomez Caldera</v>
+        <v>Samuel Escobar Posada</v>
       </c>
       <c r="C34" s="21">
         <f>+Inscritos!D32</f>
-        <v>1038130180</v>
+        <v>1038110741</v>
       </c>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
@@ -4609,11 +4717,11 @@
       </c>
       <c r="B35" s="18" t="str">
         <f>+Inscritos!B33</f>
-        <v>SARA GONZALEZ BARRIOS</v>
+        <v>Santiago  Gomez Caldera</v>
       </c>
       <c r="C35" s="21">
         <f>+Inscritos!D33</f>
-        <v>1038115649</v>
+        <v>1038130180</v>
       </c>
       <c r="D35" s="13"/>
       <c r="E35" s="13"/>
@@ -4662,11 +4770,11 @@
       </c>
       <c r="B36" s="18" t="str">
         <f>+Inscritos!B34</f>
-        <v>Sara Paulina Cardona Almanza</v>
+        <v>SARA GONZALEZ BARRIOS</v>
       </c>
       <c r="C36" s="21">
         <f>+Inscritos!D34</f>
-        <v>1038648764</v>
+        <v>1038115649</v>
       </c>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
@@ -4715,11 +4823,11 @@
       </c>
       <c r="B37" s="18" t="str">
         <f>+Inscritos!B35</f>
-        <v>Sheyla Ramirez Guerra</v>
+        <v>Sara Paulina Cardona Almanza</v>
       </c>
       <c r="C37" s="21">
         <f>+Inscritos!D35</f>
-        <v>1038118107</v>
+        <v>1038648764</v>
       </c>
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
@@ -4768,11 +4876,11 @@
       </c>
       <c r="B38" s="18" t="str">
         <f>+Inscritos!B36</f>
-        <v>Susana Tobon Ortega</v>
+        <v>Sara Paulina Cardona Almanza</v>
       </c>
       <c r="C38" s="21">
         <f>+Inscritos!D36</f>
-        <v>1020303245</v>
+        <v>1038648764</v>
       </c>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
@@ -4821,11 +4929,11 @@
       </c>
       <c r="B39" s="18" t="str">
         <f>+Inscritos!B37</f>
-        <v xml:space="preserve">Valerin Fernanda  Pérez Mejía </v>
+        <v>Sheyla Ramirez Guerra</v>
       </c>
       <c r="C39" s="21">
         <f>+Inscritos!D37</f>
-        <v>1045143166</v>
+        <v>1038118107</v>
       </c>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
@@ -4874,11 +4982,11 @@
       </c>
       <c r="B40" s="18" t="str">
         <f>+Inscritos!B38</f>
-        <v>Veleria Ruiz Garcia</v>
+        <v>Susana Tobon Ortega</v>
       </c>
       <c r="C40" s="21">
         <f>+Inscritos!D38</f>
-        <v>1038116526</v>
+        <v>1020303245</v>
       </c>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
@@ -4927,11 +5035,11 @@
       </c>
       <c r="B41" s="18" t="str">
         <f>+Inscritos!B39</f>
-        <v>Walter Antonio Perez Guzman</v>
+        <v xml:space="preserve">Valerin Fernanda  Pérez Mejía </v>
       </c>
       <c r="C41" s="21">
         <f>+Inscritos!D39</f>
-        <v>1040502849</v>
+        <v>1045143166</v>
       </c>
       <c r="D41" s="13"/>
       <c r="E41" s="13"/>
@@ -4980,11 +5088,11 @@
       </c>
       <c r="B42" s="18" t="str">
         <f>+Inscritos!B40</f>
-        <v>Xiomara yiseth Causil lopez</v>
-      </c>
-      <c r="C42" s="21" t="str">
+        <v>Veleria Ruiz Garcia</v>
+      </c>
+      <c r="C42" s="21">
         <f>+Inscritos!D40</f>
-        <v>1038115836</v>
+        <v>1038116526</v>
       </c>
       <c r="D42" s="13"/>
       <c r="E42" s="13"/>
@@ -5031,13 +5139,13 @@
       <c r="A43" s="20">
         <v>38</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="18" t="str">
         <f>+Inscritos!B41</f>
-        <v>0</v>
+        <v>Walter Antonio Perez Guzman</v>
       </c>
       <c r="C43" s="21">
         <f>+Inscritos!D41</f>
-        <v>0</v>
+        <v>1040502849</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="13"/>
@@ -5084,13 +5192,13 @@
       <c r="A44" s="20">
         <v>39</v>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="18" t="str">
         <f>+Inscritos!B42</f>
-        <v>0</v>
-      </c>
-      <c r="C44" s="21">
+        <v>Xiomara yiseth Causil lopez</v>
+      </c>
+      <c r="C44" s="21" t="str">
         <f>+Inscritos!D42</f>
-        <v>0</v>
+        <v>1038115836</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
@@ -5137,13 +5245,13 @@
       <c r="A45" s="20">
         <v>40</v>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="18" t="str">
         <f>+Inscritos!B43</f>
-        <v>0</v>
+        <v>john fredy manchego valencia</v>
       </c>
       <c r="C45" s="21">
         <f>+Inscritos!D43</f>
-        <v>0</v>
+        <v>1038125682</v>
       </c>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
@@ -5190,13 +5298,13 @@
       <c r="A46" s="20">
         <v>41</v>
       </c>
-      <c r="B46" s="18">
+      <c r="B46" s="18" t="str">
         <f>+Inscritos!B44</f>
-        <v>0</v>
+        <v>Luz Marina Mieles Nisperuza</v>
       </c>
       <c r="C46" s="21">
         <f>+Inscritos!D44</f>
-        <v>0</v>
+        <v>33104650</v>
       </c>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
@@ -6298,123 +6406,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="72.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+      <c r="Q1" s="86"/>
+      <c r="R1" s="86"/>
+      <c r="S1" s="86"/>
+      <c r="T1" s="86"/>
     </row>
     <row r="2" spans="1:20" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="45" t="str">
+      <c r="D2" s="114" t="str">
         <f>Asistencia!D2</f>
         <v>NOMBRE DOCENTE</v>
       </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="45" t="str">
+      <c r="E2" s="115"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="114" t="str">
         <f>Asistencia!I2</f>
         <v>NOMBRE DOCENTE</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="45" t="s">
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="45" t="str">
+      <c r="M2" s="115"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="115"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="114" t="str">
         <f>Asistencia!AA2</f>
         <v>NOMBRE DOCENTE</v>
       </c>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="47"/>
+      <c r="R2" s="115"/>
+      <c r="S2" s="115"/>
+      <c r="T2" s="116"/>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="58"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="65" t="s">
+      <c r="A3" s="124"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="66"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="59" t="s">
+      <c r="E3" s="132"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="94" t="s">
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="95"/>
-      <c r="N3" s="95"/>
-      <c r="O3" s="95"/>
-      <c r="P3" s="96"/>
-      <c r="Q3" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="50"/>
+      <c r="M3" s="109"/>
+      <c r="N3" s="109"/>
+      <c r="O3" s="109"/>
+      <c r="P3" s="110"/>
+      <c r="Q3" s="117" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="118"/>
+      <c r="S3" s="118"/>
+      <c r="T3" s="119"/>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="58"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="97"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="99"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="53"/>
+      <c r="A4" s="124"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="113"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="121"/>
+      <c r="S4" s="121"/>
+      <c r="T4" s="122"/>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="58"/>
-      <c r="B5" s="72"/>
-      <c r="C5" s="74"/>
+      <c r="A5" s="124"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="61"/>
       <c r="D5" s="22">
         <v>0.75</v>
       </c>
@@ -6817,11 +6925,11 @@
       </c>
       <c r="B14" s="18" t="str">
         <f>Inscritos!B12</f>
-        <v xml:space="preserve">Federman Benitez López </v>
+        <v>Elizabeth ibañez londoño</v>
       </c>
       <c r="C14" s="18">
         <f>+Inscritos!D12</f>
-        <v>1001534767</v>
+        <v>1038109715</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
@@ -6859,11 +6967,11 @@
       </c>
       <c r="B15" s="18" t="str">
         <f>Inscritos!B13</f>
-        <v>Gabriela Arenas Sánchez</v>
+        <v xml:space="preserve">Federman Benitez López </v>
       </c>
       <c r="C15" s="18">
         <f>+Inscritos!D13</f>
-        <v>1038113945</v>
+        <v>1001534767</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -6901,11 +7009,11 @@
       </c>
       <c r="B16" s="18" t="str">
         <f>Inscritos!B14</f>
-        <v>Isabella  Balza Estrada</v>
+        <v>Gabriela Arenas Sánchez</v>
       </c>
       <c r="C16" s="18">
         <f>+Inscritos!D14</f>
-        <v>1038107680</v>
+        <v>1038113945</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
@@ -6943,11 +7051,11 @@
       </c>
       <c r="B17" s="18" t="str">
         <f>Inscritos!B15</f>
-        <v>Jerónimo  Restrepo Echeberry</v>
+        <v>Isabella  Balza Estrada</v>
       </c>
       <c r="C17" s="18">
         <f>+Inscritos!D15</f>
-        <v>1040875356</v>
+        <v>1038107680</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
@@ -6985,11 +7093,11 @@
       </c>
       <c r="B18" s="18" t="str">
         <f>Inscritos!B16</f>
-        <v>Jerónimo Gil, Guerra</v>
+        <v>Jerónimo  Restrepo Echeberry</v>
       </c>
       <c r="C18" s="18">
         <f>+Inscritos!D16</f>
-        <v>1038115504</v>
+        <v>1040875356</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
@@ -7027,11 +7135,11 @@
       </c>
       <c r="B19" s="18" t="str">
         <f>Inscritos!B17</f>
-        <v>Jhon Alexander Torres Posada</v>
+        <v>Jerónimo Gil, Guerra</v>
       </c>
       <c r="C19" s="18">
         <f>+Inscritos!D17</f>
-        <v>1038117645</v>
+        <v>1038115504</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -7069,11 +7177,11 @@
       </c>
       <c r="B20" s="18" t="str">
         <f>Inscritos!B18</f>
-        <v>Johan Andrés  Arrieta Meneses</v>
+        <v>Jhon Alexander Torres Posada</v>
       </c>
       <c r="C20" s="18">
         <f>+Inscritos!D18</f>
-        <v>1038103169</v>
+        <v>1038117645</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
@@ -7111,11 +7219,11 @@
       </c>
       <c r="B21" s="18" t="str">
         <f>Inscritos!B19</f>
-        <v>Juan David Pastrana Verona</v>
+        <v>Johan Andrés  Arrieta Meneses</v>
       </c>
       <c r="C21" s="18">
         <f>+Inscritos!D19</f>
-        <v>0</v>
+        <v>1038103169</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -7153,11 +7261,11 @@
       </c>
       <c r="B22" s="18" t="str">
         <f>Inscritos!B20</f>
-        <v>juan david remolina vargas</v>
+        <v>Juan David Pastrana Verona</v>
       </c>
       <c r="C22" s="18">
         <f>+Inscritos!D20</f>
-        <v>1033261244</v>
+        <v>1067891152</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -7195,11 +7303,11 @@
       </c>
       <c r="B23" s="18" t="str">
         <f>Inscritos!B21</f>
-        <v>JUAN DIEGO  CUETO PALLARES</v>
+        <v>juan david remolina vargas</v>
       </c>
       <c r="C23" s="18">
         <f>+Inscritos!D21</f>
-        <v>1063287705</v>
+        <v>1033261244</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -7237,11 +7345,11 @@
       </c>
       <c r="B24" s="18" t="str">
         <f>Inscritos!B22</f>
-        <v xml:space="preserve">Juan Pablo Rodriguez Restrepo </v>
+        <v>Juan Diego Cueto Pallares</v>
       </c>
       <c r="C24" s="18">
         <f>+Inscritos!D22</f>
-        <v>1025894485</v>
+        <v>1063287705</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -7279,11 +7387,11 @@
       </c>
       <c r="B25" s="18" t="str">
         <f>Inscritos!B23</f>
-        <v>Manuela Carmargo Merlano</v>
+        <v xml:space="preserve">Juan Pablo Rodriguez Restrepo </v>
       </c>
       <c r="C25" s="18">
         <f>+Inscritos!D23</f>
-        <v>1038116237</v>
+        <v>1025894485</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -7321,11 +7429,11 @@
       </c>
       <c r="B26" s="18" t="str">
         <f>Inscritos!B24</f>
-        <v>MARIA INES VERGARA MANGONES</v>
+        <v>Manuela Carmargo Merlano</v>
       </c>
       <c r="C26" s="18">
         <f>+Inscritos!D24</f>
-        <v>1007470866</v>
+        <v>1038116237</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -7363,11 +7471,11 @@
       </c>
       <c r="B27" s="18" t="str">
         <f>Inscritos!B25</f>
-        <v xml:space="preserve">Martín  Araujo Vásquez </v>
+        <v>MARIA INES VERGARA MANGONES</v>
       </c>
       <c r="C27" s="18">
         <f>+Inscritos!D25</f>
-        <v>1042826278</v>
+        <v>1007470866</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -7405,11 +7513,11 @@
       </c>
       <c r="B28" s="18" t="str">
         <f>Inscritos!B26</f>
-        <v xml:space="preserve">Melany Bueno Sierra </v>
+        <v xml:space="preserve">Martín  Araujo Vásquez </v>
       </c>
       <c r="C28" s="18">
         <f>+Inscritos!D26</f>
-        <v>1038114475</v>
+        <v>1042826278</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -7447,11 +7555,11 @@
       </c>
       <c r="B29" s="18" t="str">
         <f>Inscritos!B27</f>
-        <v xml:space="preserve">Melissa Ceballos Serpa </v>
+        <v xml:space="preserve">Melany Bueno Sierra </v>
       </c>
       <c r="C29" s="18">
         <f>+Inscritos!D27</f>
-        <v>1038115335</v>
+        <v>1038114475</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -7489,11 +7597,11 @@
       </c>
       <c r="B30" s="18" t="str">
         <f>Inscritos!B28</f>
-        <v xml:space="preserve">Nikoll Paternina Sánchez </v>
+        <v xml:space="preserve">Melissa Ceballos Serpa </v>
       </c>
       <c r="C30" s="18">
         <f>+Inscritos!D28</f>
-        <v>1065889467</v>
+        <v>1038115335</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -7531,11 +7639,11 @@
       </c>
       <c r="B31" s="18" t="str">
         <f>Inscritos!B29</f>
-        <v>Rousse Peralta</v>
+        <v xml:space="preserve">Nikoll Paternina Sánchez </v>
       </c>
       <c r="C31" s="18">
         <f>+Inscritos!D29</f>
-        <v>1003305257</v>
+        <v>1065889467</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -7573,11 +7681,11 @@
       </c>
       <c r="B32" s="18" t="str">
         <f>Inscritos!B30</f>
-        <v xml:space="preserve">Samuel  Muñoz </v>
+        <v>Rousse Peralta</v>
       </c>
       <c r="C32" s="18">
         <f>+Inscritos!D30</f>
-        <v>1066517127</v>
+        <v>1003305257</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -7615,11 +7723,11 @@
       </c>
       <c r="B33" s="18" t="str">
         <f>Inscritos!B31</f>
-        <v>Samuel Escobar Posada</v>
+        <v xml:space="preserve">Samuel  Muñoz </v>
       </c>
       <c r="C33" s="18">
         <f>+Inscritos!D31</f>
-        <v>1038110741</v>
+        <v>1066517127</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -7657,11 +7765,11 @@
       </c>
       <c r="B34" s="18" t="str">
         <f>Inscritos!B32</f>
-        <v>Santiago  Gomez Caldera</v>
+        <v>Samuel Escobar Posada</v>
       </c>
       <c r="C34" s="18">
         <f>+Inscritos!D32</f>
-        <v>1038130180</v>
+        <v>1038110741</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -7699,11 +7807,11 @@
       </c>
       <c r="B35" s="18" t="str">
         <f>Inscritos!B33</f>
-        <v>SARA GONZALEZ BARRIOS</v>
+        <v>Santiago  Gomez Caldera</v>
       </c>
       <c r="C35" s="18">
         <f>+Inscritos!D33</f>
-        <v>1038115649</v>
+        <v>1038130180</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -7741,11 +7849,11 @@
       </c>
       <c r="B36" s="18" t="str">
         <f>Inscritos!B34</f>
-        <v>Sara Paulina Cardona Almanza</v>
+        <v>SARA GONZALEZ BARRIOS</v>
       </c>
       <c r="C36" s="18">
         <f>+Inscritos!D34</f>
-        <v>1038648764</v>
+        <v>1038115649</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -7783,11 +7891,11 @@
       </c>
       <c r="B37" s="18" t="str">
         <f>Inscritos!B35</f>
-        <v>Sheyla Ramirez Guerra</v>
+        <v>Sara Paulina Cardona Almanza</v>
       </c>
       <c r="C37" s="18">
         <f>+Inscritos!D35</f>
-        <v>1038118107</v>
+        <v>1038648764</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -7825,11 +7933,11 @@
       </c>
       <c r="B38" s="18" t="str">
         <f>Inscritos!B36</f>
-        <v>Susana Tobon Ortega</v>
+        <v>Sara Paulina Cardona Almanza</v>
       </c>
       <c r="C38" s="18">
         <f>+Inscritos!D36</f>
-        <v>1020303245</v>
+        <v>1038648764</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -7867,11 +7975,11 @@
       </c>
       <c r="B39" s="18" t="str">
         <f>Inscritos!B37</f>
-        <v xml:space="preserve">Valerin Fernanda  Pérez Mejía </v>
+        <v>Sheyla Ramirez Guerra</v>
       </c>
       <c r="C39" s="18">
         <f>+Inscritos!D37</f>
-        <v>1045143166</v>
+        <v>1038118107</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -7909,11 +8017,11 @@
       </c>
       <c r="B40" s="18" t="str">
         <f>Inscritos!B38</f>
-        <v>Veleria Ruiz Garcia</v>
+        <v>Susana Tobon Ortega</v>
       </c>
       <c r="C40" s="18">
         <f>+Inscritos!D38</f>
-        <v>1038116526</v>
+        <v>1020303245</v>
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -7951,11 +8059,11 @@
       </c>
       <c r="B41" s="18" t="str">
         <f>Inscritos!B39</f>
-        <v>Walter Antonio Perez Guzman</v>
+        <v xml:space="preserve">Valerin Fernanda  Pérez Mejía </v>
       </c>
       <c r="C41" s="18">
         <f>+Inscritos!D39</f>
-        <v>1040502849</v>
+        <v>1045143166</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -7993,11 +8101,11 @@
       </c>
       <c r="B42" s="18" t="str">
         <f>Inscritos!B40</f>
-        <v>Xiomara yiseth Causil lopez</v>
-      </c>
-      <c r="C42" s="18" t="str">
+        <v>Veleria Ruiz Garcia</v>
+      </c>
+      <c r="C42" s="18">
         <f>+Inscritos!D40</f>
-        <v>1038115836</v>
+        <v>1038116526</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -8033,13 +8141,13 @@
       <c r="A43" s="10">
         <v>38</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="18" t="str">
         <f>Inscritos!B41</f>
-        <v>0</v>
+        <v>Walter Antonio Perez Guzman</v>
       </c>
       <c r="C43" s="18">
         <f>+Inscritos!D41</f>
-        <v>0</v>
+        <v>1040502849</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -8075,13 +8183,13 @@
       <c r="A44" s="10">
         <v>39</v>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="18" t="str">
         <f>Inscritos!B42</f>
-        <v>0</v>
-      </c>
-      <c r="C44" s="18">
+        <v>Xiomara yiseth Causil lopez</v>
+      </c>
+      <c r="C44" s="18" t="str">
         <f>+Inscritos!D42</f>
-        <v>0</v>
+        <v>1038115836</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -8117,13 +8225,13 @@
       <c r="A45" s="10">
         <v>40</v>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="18" t="str">
         <f>Inscritos!B43</f>
-        <v>0</v>
+        <v>john fredy manchego valencia</v>
       </c>
       <c r="C45" s="18">
         <f>+Inscritos!D43</f>
-        <v>0</v>
+        <v>1038125682</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -8159,13 +8267,13 @@
       <c r="A46" s="10">
         <v>41</v>
       </c>
-      <c r="B46" s="18">
+      <c r="B46" s="18" t="str">
         <f>Inscritos!B44</f>
-        <v>0</v>
+        <v>Luz Marina Mieles Nisperuza</v>
       </c>
       <c r="C46" s="18">
         <f>+Inscritos!D44</f>
-        <v>0</v>
+        <v>33104650</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
@@ -8996,186 +9104,195 @@
       </c>
     </row>
     <row r="66" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D66" s="79" t="s">
+      <c r="D66" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="E66" s="82" t="s">
+      <c r="E66" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="G66" s="76" t="s">
+      <c r="G66" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="H66" s="88" t="s">
+      <c r="H66" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="I66" s="88" t="s">
+      <c r="I66" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="J66" s="76" t="s">
+      <c r="J66" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="L66" s="54" t="s">
+      <c r="L66" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="M66" s="85" t="s">
+      <c r="M66" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="N66" s="85" t="s">
+      <c r="N66" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="O66" s="54" t="s">
+      <c r="O66" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="Q66" s="91" t="s">
+      <c r="Q66" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="R66" s="91" t="s">
+      <c r="R66" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="S66" s="91" t="s">
+      <c r="S66" s="105" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D67" s="80"/>
-      <c r="E67" s="83"/>
-      <c r="G67" s="77"/>
-      <c r="H67" s="89"/>
-      <c r="I67" s="89"/>
-      <c r="J67" s="77"/>
-      <c r="L67" s="55"/>
-      <c r="M67" s="86"/>
-      <c r="N67" s="86"/>
-      <c r="O67" s="55"/>
-      <c r="Q67" s="92"/>
-      <c r="R67" s="92"/>
-      <c r="S67" s="92"/>
+      <c r="D67" s="91"/>
+      <c r="E67" s="94"/>
+      <c r="G67" s="88"/>
+      <c r="H67" s="103"/>
+      <c r="I67" s="103"/>
+      <c r="J67" s="88"/>
+      <c r="L67" s="97"/>
+      <c r="M67" s="100"/>
+      <c r="N67" s="100"/>
+      <c r="O67" s="97"/>
+      <c r="Q67" s="106"/>
+      <c r="R67" s="106"/>
+      <c r="S67" s="106"/>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D68" s="80"/>
-      <c r="E68" s="83"/>
-      <c r="G68" s="77"/>
-      <c r="H68" s="89"/>
-      <c r="I68" s="89"/>
-      <c r="J68" s="77"/>
-      <c r="L68" s="55"/>
-      <c r="M68" s="86"/>
-      <c r="N68" s="86"/>
-      <c r="O68" s="55"/>
-      <c r="Q68" s="92"/>
-      <c r="R68" s="92"/>
-      <c r="S68" s="92"/>
+      <c r="D68" s="91"/>
+      <c r="E68" s="94"/>
+      <c r="G68" s="88"/>
+      <c r="H68" s="103"/>
+      <c r="I68" s="103"/>
+      <c r="J68" s="88"/>
+      <c r="L68" s="97"/>
+      <c r="M68" s="100"/>
+      <c r="N68" s="100"/>
+      <c r="O68" s="97"/>
+      <c r="Q68" s="106"/>
+      <c r="R68" s="106"/>
+      <c r="S68" s="106"/>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D69" s="80"/>
-      <c r="E69" s="83"/>
-      <c r="G69" s="77"/>
-      <c r="H69" s="89"/>
-      <c r="I69" s="89"/>
-      <c r="J69" s="77"/>
-      <c r="L69" s="55"/>
-      <c r="M69" s="86"/>
-      <c r="N69" s="86"/>
-      <c r="O69" s="55"/>
-      <c r="Q69" s="92"/>
-      <c r="R69" s="92"/>
-      <c r="S69" s="92"/>
+      <c r="D69" s="91"/>
+      <c r="E69" s="94"/>
+      <c r="G69" s="88"/>
+      <c r="H69" s="103"/>
+      <c r="I69" s="103"/>
+      <c r="J69" s="88"/>
+      <c r="L69" s="97"/>
+      <c r="M69" s="100"/>
+      <c r="N69" s="100"/>
+      <c r="O69" s="97"/>
+      <c r="Q69" s="106"/>
+      <c r="R69" s="106"/>
+      <c r="S69" s="106"/>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D70" s="80"/>
-      <c r="E70" s="83"/>
-      <c r="G70" s="77"/>
-      <c r="H70" s="89"/>
-      <c r="I70" s="89"/>
-      <c r="J70" s="77"/>
-      <c r="L70" s="55"/>
-      <c r="M70" s="86"/>
-      <c r="N70" s="86"/>
-      <c r="O70" s="55"/>
-      <c r="Q70" s="92"/>
-      <c r="R70" s="92"/>
-      <c r="S70" s="92"/>
+      <c r="D70" s="91"/>
+      <c r="E70" s="94"/>
+      <c r="G70" s="88"/>
+      <c r="H70" s="103"/>
+      <c r="I70" s="103"/>
+      <c r="J70" s="88"/>
+      <c r="L70" s="97"/>
+      <c r="M70" s="100"/>
+      <c r="N70" s="100"/>
+      <c r="O70" s="97"/>
+      <c r="Q70" s="106"/>
+      <c r="R70" s="106"/>
+      <c r="S70" s="106"/>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D71" s="80"/>
-      <c r="E71" s="83"/>
-      <c r="G71" s="77"/>
-      <c r="H71" s="89"/>
-      <c r="I71" s="89"/>
-      <c r="J71" s="77"/>
-      <c r="L71" s="55"/>
-      <c r="M71" s="86"/>
-      <c r="N71" s="86"/>
-      <c r="O71" s="55"/>
-      <c r="Q71" s="92"/>
-      <c r="R71" s="92"/>
-      <c r="S71" s="92"/>
+      <c r="D71" s="91"/>
+      <c r="E71" s="94"/>
+      <c r="G71" s="88"/>
+      <c r="H71" s="103"/>
+      <c r="I71" s="103"/>
+      <c r="J71" s="88"/>
+      <c r="L71" s="97"/>
+      <c r="M71" s="100"/>
+      <c r="N71" s="100"/>
+      <c r="O71" s="97"/>
+      <c r="Q71" s="106"/>
+      <c r="R71" s="106"/>
+      <c r="S71" s="106"/>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D72" s="80"/>
-      <c r="E72" s="83"/>
-      <c r="G72" s="77"/>
-      <c r="H72" s="89"/>
-      <c r="I72" s="89"/>
-      <c r="J72" s="77"/>
-      <c r="L72" s="55"/>
-      <c r="M72" s="86"/>
-      <c r="N72" s="86"/>
-      <c r="O72" s="55"/>
-      <c r="Q72" s="92"/>
-      <c r="R72" s="92"/>
-      <c r="S72" s="92"/>
+      <c r="D72" s="91"/>
+      <c r="E72" s="94"/>
+      <c r="G72" s="88"/>
+      <c r="H72" s="103"/>
+      <c r="I72" s="103"/>
+      <c r="J72" s="88"/>
+      <c r="L72" s="97"/>
+      <c r="M72" s="100"/>
+      <c r="N72" s="100"/>
+      <c r="O72" s="97"/>
+      <c r="Q72" s="106"/>
+      <c r="R72" s="106"/>
+      <c r="S72" s="106"/>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D73" s="80"/>
-      <c r="E73" s="83"/>
-      <c r="G73" s="77"/>
-      <c r="H73" s="89"/>
-      <c r="I73" s="89"/>
-      <c r="J73" s="77"/>
-      <c r="L73" s="55"/>
-      <c r="M73" s="86"/>
-      <c r="N73" s="86"/>
-      <c r="O73" s="55"/>
-      <c r="Q73" s="92"/>
-      <c r="R73" s="92"/>
-      <c r="S73" s="92"/>
+      <c r="D73" s="91"/>
+      <c r="E73" s="94"/>
+      <c r="G73" s="88"/>
+      <c r="H73" s="103"/>
+      <c r="I73" s="103"/>
+      <c r="J73" s="88"/>
+      <c r="L73" s="97"/>
+      <c r="M73" s="100"/>
+      <c r="N73" s="100"/>
+      <c r="O73" s="97"/>
+      <c r="Q73" s="106"/>
+      <c r="R73" s="106"/>
+      <c r="S73" s="106"/>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D74" s="80"/>
-      <c r="E74" s="83"/>
-      <c r="G74" s="77"/>
-      <c r="H74" s="89"/>
-      <c r="I74" s="89"/>
-      <c r="J74" s="77"/>
-      <c r="L74" s="55"/>
-      <c r="M74" s="86"/>
-      <c r="N74" s="86"/>
-      <c r="O74" s="55"/>
-      <c r="Q74" s="92"/>
-      <c r="R74" s="92"/>
-      <c r="S74" s="92"/>
+      <c r="D74" s="91"/>
+      <c r="E74" s="94"/>
+      <c r="G74" s="88"/>
+      <c r="H74" s="103"/>
+      <c r="I74" s="103"/>
+      <c r="J74" s="88"/>
+      <c r="L74" s="97"/>
+      <c r="M74" s="100"/>
+      <c r="N74" s="100"/>
+      <c r="O74" s="97"/>
+      <c r="Q74" s="106"/>
+      <c r="R74" s="106"/>
+      <c r="S74" s="106"/>
     </row>
     <row r="75" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D75" s="81"/>
-      <c r="E75" s="84"/>
-      <c r="G75" s="78"/>
-      <c r="H75" s="90"/>
-      <c r="I75" s="90"/>
-      <c r="J75" s="78"/>
-      <c r="L75" s="56"/>
-      <c r="M75" s="87"/>
-      <c r="N75" s="87"/>
-      <c r="O75" s="56"/>
-      <c r="Q75" s="93"/>
-      <c r="R75" s="93"/>
-      <c r="S75" s="93"/>
+      <c r="D75" s="92"/>
+      <c r="E75" s="95"/>
+      <c r="G75" s="89"/>
+      <c r="H75" s="104"/>
+      <c r="I75" s="104"/>
+      <c r="J75" s="89"/>
+      <c r="L75" s="98"/>
+      <c r="M75" s="101"/>
+      <c r="N75" s="101"/>
+      <c r="O75" s="98"/>
+      <c r="Q75" s="107"/>
+      <c r="R75" s="107"/>
+      <c r="S75" s="107"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:T60">
     <sortCondition ref="B6"/>
   </sortState>
   <mergeCells count="25">
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="Q3:T4"/>
+    <mergeCell ref="O66:O75"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="G3:K4"/>
+    <mergeCell ref="D3:F4"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C2:C5"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="J66:J75"/>
     <mergeCell ref="D66:D75"/>
@@ -9192,15 +9309,6 @@
     <mergeCell ref="I66:I75"/>
     <mergeCell ref="Q2:T2"/>
     <mergeCell ref="L2:P2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="Q3:T4"/>
-    <mergeCell ref="O66:O75"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="G3:K4"/>
-    <mergeCell ref="D3:F4"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
